--- a/tests/Import/fixtures/14_encabezado_corrido.xlsx
+++ b/tests/Import/fixtures/14_encabezado_corrido.xlsx
@@ -15,12 +15,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>LISTA DE PRECIOS AGOSTO 2026</t>
   </si>
   <si>
+    <t>Vigencia desde:</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
     <t>Distribuidora Bianchi S.A.</t>
+  </si>
+  <si>
+    <t>30712345679</t>
   </si>
   <si>
     <t>codigo_de_barras</t>
@@ -454,50 +463,59 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>100.0</v>
@@ -509,21 +527,21 @@
         <v>10.0</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>200.0</v>
@@ -535,21 +553,21 @@
         <v>20.0</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>300.0</v>
@@ -561,21 +579,21 @@
         <v>30.0</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>400.0</v>
@@ -587,21 +605,21 @@
         <v>40.0</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>500.0</v>
@@ -613,7 +631,7 @@
         <v>50.0</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
